--- a/configs/wpc/5/vail.xlsx
+++ b/configs/wpc/5/vail.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="164">
   <si>
     <t>Content</t>
   </si>
@@ -1559,17 +1559,17 @@
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>47</v>
+      <c r="A39" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B39" s="1" t="str">
+        <v>puer_tea_gQP_1_tQP_1.ply</v>
       </c>
       <c r="C39">
-        <v>87.624839242731795</v>
-      </c>
-      <c r="D39" t="s">
-        <v>9</v>
+        <v>77.914700954506</v>
+      </c>
+      <c r="D39" t="str">
+        <v>V-PCC</v>
       </c>
       <c r="E39">
         <v>1</v>
@@ -1579,17 +1579,17 @@
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>46</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>48</v>
+      <c r="A40" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B40" s="1" t="str">
+        <v>puer_tea_gQP_1_tQP_2.ply</v>
       </c>
       <c r="C40">
-        <v>69.934018210425805</v>
-      </c>
-      <c r="D40" t="s">
-        <v>9</v>
+        <v>75.4444591024422</v>
+      </c>
+      <c r="D40" t="str">
+        <v>V-PCC</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -1599,17 +1599,17 @@
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>46</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>49</v>
+      <c r="A41" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B41" s="1" t="str">
+        <v>puer_tea_gQP_1_tQP_3.ply</v>
       </c>
       <c r="C41">
-        <v>55.866480079135599</v>
-      </c>
-      <c r="D41" t="s">
-        <v>9</v>
+        <v>51.2988745216774</v>
+      </c>
+      <c r="D41" t="str">
+        <v>V-PCC</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -1619,17 +1619,17 @@
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>46</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>50</v>
+      <c r="A42" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B42" s="1" t="str">
+        <v>puer_tea_gQP_2_tQP_1.ply</v>
       </c>
       <c r="C42">
-        <v>77.640064800645206</v>
-      </c>
-      <c r="D42" t="s">
-        <v>9</v>
+        <v>62.5054541432411</v>
+      </c>
+      <c r="D42" t="str">
+        <v>V-PCC</v>
       </c>
       <c r="E42">
         <v>2</v>
@@ -1639,17 +1639,17 @@
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>46</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>51</v>
+      <c r="A43" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B43" s="1" t="str">
+        <v>puer_tea_gQP_2_tQP_2.ply</v>
       </c>
       <c r="C43">
-        <v>61.726469269953199</v>
-      </c>
-      <c r="D43" t="s">
-        <v>9</v>
+        <v>63.4256547659898</v>
+      </c>
+      <c r="D43" t="str">
+        <v>V-PCC</v>
       </c>
       <c r="E43">
         <v>2</v>
@@ -1659,17 +1659,17 @@
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>46</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>52</v>
+      <c r="A44" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B44" s="1" t="str">
+        <v>puer_tea_gQP_2_tQP_3.ply</v>
       </c>
       <c r="C44">
-        <v>50.222841156529199</v>
-      </c>
-      <c r="D44" t="s">
-        <v>9</v>
+        <v>48.9932846071129</v>
+      </c>
+      <c r="D44" t="str">
+        <v>V-PCC</v>
       </c>
       <c r="E44">
         <v>2</v>
@@ -1679,17 +1679,17 @@
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>46</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>53</v>
+      <c r="A45" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B45" s="1" t="str">
+        <v>puer_tea_gQP_3_tQP_1.ply</v>
       </c>
       <c r="C45">
-        <v>34.473648144851303</v>
-      </c>
-      <c r="D45" t="s">
-        <v>9</v>
+        <v>49.2533031787853</v>
+      </c>
+      <c r="D45" t="str">
+        <v>V-PCC</v>
       </c>
       <c r="E45">
         <v>3</v>
@@ -1699,17 +1699,17 @@
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>46</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>54</v>
+      <c r="A46" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B46" s="1" t="str">
+        <v>puer_tea_gQP_3_tQP_2.ply</v>
       </c>
       <c r="C46">
-        <v>27.411619554346501</v>
-      </c>
-      <c r="D46" t="s">
-        <v>9</v>
+        <v>42.0841687809331</v>
+      </c>
+      <c r="D46" t="str">
+        <v>V-PCC</v>
       </c>
       <c r="E46">
         <v>3</v>
@@ -1719,17 +1719,17 @@
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>46</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>55</v>
+      <c r="A47" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B47" s="1" t="str">
+        <v>puer_tea_gQP_3_tQP_3.ply</v>
       </c>
       <c r="C47">
-        <v>30.231397565594101</v>
-      </c>
-      <c r="D47" t="s">
-        <v>9</v>
+        <v>37.3107135366479</v>
+      </c>
+      <c r="D47" t="str">
+        <v>V-PCC</v>
       </c>
       <c r="E47">
         <v>3</v>
@@ -1739,17 +1739,17 @@
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>46</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>56</v>
+      <c r="A48" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B48" s="1" t="str">
+        <v>puer_tea_gsigma_0_tsigma_16.ply</v>
       </c>
       <c r="C48">
-        <v>57.425103805969002</v>
-      </c>
-      <c r="D48" t="s">
-        <v>19</v>
+        <v>48.6325940292948</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Gaussian noise</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -1759,17 +1759,17 @@
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>46</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>57</v>
+      <c r="A49" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B49" s="1" t="str">
+        <v>puer_tea_gsigma_0_tsigma_32.ply</v>
       </c>
       <c r="C49">
-        <v>40.190717226665001</v>
-      </c>
-      <c r="D49" t="s">
-        <v>19</v>
+        <v>34.7408576952058</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Gaussian noise</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -1779,17 +1779,17 @@
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>46</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>58</v>
+      <c r="A50" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B50" s="1" t="str">
+        <v>puer_tea_gsigma_0_tsigma_8.ply</v>
       </c>
       <c r="C50">
-        <v>77.762268328402797</v>
-      </c>
-      <c r="D50" t="s">
-        <v>19</v>
+        <v>79.4766933491598</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Gaussian noise</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -1799,17 +1799,17 @@
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>46</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>59</v>
+      <c r="A51" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B51" s="1" t="str">
+        <v>puer_tea_gsigma_2_tsigma_16.ply</v>
       </c>
       <c r="C51">
-        <v>53.131719170366402</v>
-      </c>
-      <c r="D51" t="s">
-        <v>19</v>
+        <v>32.5523097966144</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Gaussian noise</v>
       </c>
       <c r="E51">
         <v>2</v>
@@ -1819,17 +1819,17 @@
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>46</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>60</v>
+      <c r="A52" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B52" s="1" t="str">
+        <v>puer_tea_gsigma_2_tsigma_32.ply</v>
       </c>
       <c r="C52">
-        <v>31.3681861609079</v>
-      </c>
-      <c r="D52" t="s">
-        <v>19</v>
+        <v>27.4135990964935</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Gaussian noise</v>
       </c>
       <c r="E52">
         <v>2</v>
@@ -1839,17 +1839,17 @@
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>46</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>61</v>
+      <c r="A53" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B53" s="1" t="str">
+        <v>puer_tea_gsigma_2_tsigma_8.ply</v>
       </c>
       <c r="C53">
-        <v>64.162296703930707</v>
-      </c>
-      <c r="D53" t="s">
-        <v>19</v>
+        <v>43.4702655634764</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Gaussian noise</v>
       </c>
       <c r="E53">
         <v>2</v>
@@ -1859,17 +1859,17 @@
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>46</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>62</v>
+      <c r="A54" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B54" s="1" t="str">
+        <v>puer_tea_gsigma_4_tsigma_16.ply</v>
       </c>
       <c r="C54">
-        <v>44.404701609065597</v>
-      </c>
-      <c r="D54" t="s">
-        <v>19</v>
+        <v>22.9869495082541</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Gaussian noise</v>
       </c>
       <c r="E54">
         <v>4</v>
@@ -1879,17 +1879,17 @@
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>46</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>63</v>
+      <c r="A55" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B55" s="1" t="str">
+        <v>puer_tea_gsigma_4_tsigma_32.ply</v>
       </c>
       <c r="C55">
-        <v>27.325841588284302</v>
-      </c>
-      <c r="D55" t="s">
-        <v>19</v>
+        <v>17.40818679622</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Gaussian noise</v>
       </c>
       <c r="E55">
         <v>4</v>
@@ -1899,17 +1899,17 @@
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>46</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>64</v>
+      <c r="A56" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B56" s="1" t="str">
+        <v>puer_tea_gsigma_4_tsigma_8.ply</v>
       </c>
       <c r="C56">
-        <v>47.857172990996801</v>
-      </c>
-      <c r="D56" t="s">
-        <v>19</v>
+        <v>24.0019876904387</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Gaussian noise</v>
       </c>
       <c r="E56">
         <v>4</v>
@@ -1919,17 +1919,17 @@
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>46</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>65</v>
+      <c r="A57" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B57" s="1" t="str">
+        <v>puer_tea_level_7.ply</v>
       </c>
       <c r="C57">
-        <v>8.7934596229941793</v>
-      </c>
-      <c r="D57" t="s">
-        <v>29</v>
+        <v>3.15346252854002</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Downsampling</v>
       </c>
       <c r="E57">
         <v>7</v>
@@ -1939,17 +1939,17 @@
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>46</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>66</v>
+      <c r="A58" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B58" s="1" t="str">
+        <v>puer_tea_level_8.ply</v>
       </c>
       <c r="C58">
-        <v>16.030603036989699</v>
-      </c>
-      <c r="D58" t="s">
-        <v>29</v>
+        <v>16.2603349265675</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Downsampling</v>
       </c>
       <c r="E58">
         <v>8</v>
@@ -1959,17 +1959,17 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>46</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>67</v>
+      <c r="A59" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B59" s="1" t="str">
+        <v>puer_tea_level_9.ply</v>
       </c>
       <c r="C59">
-        <v>74.681149424790405</v>
-      </c>
-      <c r="D59" t="s">
-        <v>29</v>
+        <v>77.8432664101668</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Downsampling</v>
       </c>
       <c r="E59">
         <v>9</v>
@@ -1979,17 +1979,17 @@
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>46</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>161</v>
+      <c r="A60" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B60" s="1" t="str">
+        <v>puer_tea_pqs_1_qs_16_rounded.ply</v>
       </c>
       <c r="C60">
-        <v>90.0384616380816</v>
-      </c>
-      <c r="D60" t="s">
-        <v>32</v>
+        <v>88.7792248817324</v>
+      </c>
+      <c r="D60" t="str">
+        <v>G-PCC (O)/L-PCC</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -1999,17 +1999,17 @@
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>46</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>157</v>
+      <c r="A61" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B61" s="1" t="str">
+        <v>puer_tea_pqs_1_qs_32_rounded.ply</v>
       </c>
       <c r="C61">
-        <v>63.729456137390002</v>
-      </c>
-      <c r="D61" t="s">
-        <v>32</v>
+        <v>57.8307403442314</v>
+      </c>
+      <c r="D61" t="str">
+        <v>G-PCC (O)/L-PCC</v>
       </c>
       <c r="E61">
         <v>1</v>
@@ -2019,17 +2019,17 @@
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>46</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>153</v>
+      <c r="A62" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B62" s="1" t="str">
+        <v>puer_tea_pqs_1_qs_48_rounded.ply</v>
       </c>
       <c r="C62">
-        <v>27.078460181113101</v>
-      </c>
-      <c r="D62" t="s">
-        <v>32</v>
+        <v>53.8310144289387</v>
+      </c>
+      <c r="D62" t="str">
+        <v>G-PCC (O)/L-PCC</v>
       </c>
       <c r="E62">
         <v>1</v>
@@ -2039,17 +2039,17 @@
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>46</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>149</v>
+      <c r="A63" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B63" s="1" t="str">
+        <v>puer_tea_pqs_1_qs_64_rounded.ply</v>
       </c>
       <c r="C63">
-        <v>14.403348613322301</v>
-      </c>
-      <c r="D63" t="s">
-        <v>32</v>
+        <v>48.0135449671769</v>
+      </c>
+      <c r="D63" t="str">
+        <v>G-PCC (O)/L-PCC</v>
       </c>
       <c r="E63">
         <v>1</v>
@@ -2058,24 +2058,24 @@
         <v>64</v>
       </c>
       <c r="H63">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I63">
         <v>35</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>46</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>68</v>
+      <c r="A64" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B64" s="1" t="str">
+        <v>puer_tea_tsl_4_tqs_128.ply</v>
       </c>
       <c r="C64">
-        <v>42.188692944373997</v>
-      </c>
-      <c r="D64" t="s">
-        <v>34</v>
+        <v>26.8199135306378</v>
+      </c>
+      <c r="D64" t="str">
+        <v>G-PCC (T)/S-PCC</v>
       </c>
       <c r="E64">
         <v>4</v>
@@ -2084,24 +2084,24 @@
         <v>128</v>
       </c>
       <c r="H64">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I64">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>46</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>69</v>
+      <c r="A65" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B65" s="1" t="str">
+        <v>puer_tea_tsl_4_tqs_256.ply</v>
       </c>
       <c r="C65">
-        <v>33.130068692908601</v>
-      </c>
-      <c r="D65" t="s">
-        <v>34</v>
+        <v>12.1998153379797</v>
+      </c>
+      <c r="D65" t="str">
+        <v>G-PCC (T)/S-PCC</v>
       </c>
       <c r="E65">
         <v>4</v>
@@ -2110,24 +2110,24 @@
         <v>256</v>
       </c>
       <c r="H65">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I65">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>46</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>70</v>
+      <c r="A66" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B66" s="1" t="str">
+        <v>puer_tea_tsl_4_tqs_512.ply</v>
       </c>
       <c r="C66">
-        <v>26.6104175998077</v>
-      </c>
-      <c r="D66" t="s">
-        <v>34</v>
+        <v>5.84222472057741</v>
+      </c>
+      <c r="D66" t="str">
+        <v>G-PCC (T)/S-PCC</v>
       </c>
       <c r="E66">
         <v>4</v>
@@ -2136,24 +2136,24 @@
         <v>512</v>
       </c>
       <c r="H66">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I66">
         <v>35</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>46</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>71</v>
+      <c r="A67" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B67" s="1" t="str">
+        <v>puer_tea_tsl_4_tqs_64.ply</v>
       </c>
       <c r="C67">
-        <v>61.903997287238901</v>
-      </c>
-      <c r="D67" t="s">
-        <v>34</v>
+        <v>22.6305666322368</v>
+      </c>
+      <c r="D67" t="str">
+        <v>G-PCC (T)/S-PCC</v>
       </c>
       <c r="E67">
         <v>4</v>
@@ -2162,24 +2162,24 @@
         <v>64</v>
       </c>
       <c r="H67">
+        <v>45</v>
+      </c>
+      <c r="I67">
         <v>40</v>
       </c>
-      <c r="I67">
-        <v>45</v>
-      </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>46</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>72</v>
+      <c r="A68" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B68" s="1" t="str">
+        <v>puer_tea_tsl_6_tqs_128.ply</v>
       </c>
       <c r="C68">
-        <v>64.2706535471644</v>
-      </c>
-      <c r="D68" t="s">
-        <v>34</v>
+        <v>62.9862121483958</v>
+      </c>
+      <c r="D68" t="str">
+        <v>G-PCC (T)/S-PCC</v>
       </c>
       <c r="E68">
         <v>6</v>
@@ -2188,24 +2188,24 @@
         <v>128</v>
       </c>
       <c r="H68">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I68">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>46</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>73</v>
+      <c r="A69" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B69" s="1" t="str">
+        <v>puer_tea_tsl_6_tqs_256.ply</v>
       </c>
       <c r="C69">
-        <v>41.866339724841502</v>
-      </c>
-      <c r="D69" t="s">
-        <v>34</v>
+        <v>28.5558617819512</v>
+      </c>
+      <c r="D69" t="str">
+        <v>G-PCC (T)/S-PCC</v>
       </c>
       <c r="E69">
         <v>6</v>
@@ -2221,17 +2221,17 @@
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>46</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>74</v>
+      <c r="A70" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B70" s="1" t="str">
+        <v>puer_tea_tsl_6_tqs_512.ply</v>
       </c>
       <c r="C70">
-        <v>29.742165657412102</v>
-      </c>
-      <c r="D70" t="s">
-        <v>34</v>
+        <v>16.5995484743701</v>
+      </c>
+      <c r="D70" t="str">
+        <v>G-PCC (T)/S-PCC</v>
       </c>
       <c r="E70">
         <v>6</v>
@@ -2243,21 +2243,21 @@
         <v>50</v>
       </c>
       <c r="I70">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>46</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>75</v>
+      <c r="A71" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B71" s="1" t="str">
+        <v>puer_tea_tsl_6_tqs_64.ply</v>
       </c>
       <c r="C71">
-        <v>75.533957334095305</v>
-      </c>
-      <c r="D71" t="s">
-        <v>34</v>
+        <v>86.8804487654727</v>
+      </c>
+      <c r="D71" t="str">
+        <v>G-PCC (T)/S-PCC</v>
       </c>
       <c r="E71">
         <v>6</v>
@@ -2269,21 +2269,21 @@
         <v>50</v>
       </c>
       <c r="I71">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>46</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>76</v>
+      <c r="A72" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B72" s="1" t="str">
+        <v>puer_tea_tsl_8_tqs_128.ply</v>
       </c>
       <c r="C72">
-        <v>79.765266764881801</v>
-      </c>
-      <c r="D72" t="s">
-        <v>34</v>
+        <v>61.7974566844332</v>
+      </c>
+      <c r="D72" t="str">
+        <v>G-PCC (T)/S-PCC</v>
       </c>
       <c r="E72">
         <v>8</v>
@@ -2293,17 +2293,17 @@
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>46</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>77</v>
+      <c r="A73" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B73" s="1" t="str">
+        <v>puer_tea_tsl_8_tqs_256.ply</v>
       </c>
       <c r="C73">
-        <v>43.9879089599129</v>
-      </c>
-      <c r="D73" t="s">
-        <v>34</v>
+        <v>36.1136410683924</v>
+      </c>
+      <c r="D73" t="str">
+        <v>G-PCC (T)/S-PCC</v>
       </c>
       <c r="E73">
         <v>8</v>
@@ -2313,17 +2313,17 @@
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>46</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>78</v>
+      <c r="A74" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B74" s="1" t="str">
+        <v>puer_tea_tsl_8_tqs_512.ply</v>
       </c>
       <c r="C74">
-        <v>27.744396085480201</v>
-      </c>
-      <c r="D74" t="s">
-        <v>34</v>
+        <v>21.5459093155011</v>
+      </c>
+      <c r="D74" t="str">
+        <v>G-PCC (T)/S-PCC</v>
       </c>
       <c r="E74">
         <v>8</v>
@@ -2333,17 +2333,17 @@
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>46</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>79</v>
+      <c r="A75" t="str">
+        <v>puer_tea</v>
+      </c>
+      <c r="B75" s="1" t="str">
+        <v>puer_tea_tsl_8_tqs_64.ply</v>
       </c>
       <c r="C75">
-        <v>92.851369077875404</v>
-      </c>
-      <c r="D75" t="s">
-        <v>34</v>
+        <v>79.8453305174932</v>
+      </c>
+      <c r="D75" t="str">
+        <v>G-PCC (T)/S-PCC</v>
       </c>
       <c r="E75">
         <v>8</v>
